--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/196.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/196.xlsx
@@ -426,13 +426,13 @@
         <v>-3.821061264851463</v>
       </c>
       <c r="E2">
-        <v>-17.33662630023849</v>
+        <v>-14.58742595797387</v>
       </c>
       <c r="F2">
-        <v>-3.458860663147886</v>
+        <v>-4.259890284920202</v>
       </c>
       <c r="G2">
-        <v>-9.928638414223315</v>
+        <v>-8.057753124160529</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-3.779678090941371</v>
       </c>
       <c r="E3">
-        <v>-17.71897441765411</v>
+        <v>-15.35673217934493</v>
       </c>
       <c r="F3">
-        <v>-3.255418599224744</v>
+        <v>-4.306723692772278</v>
       </c>
       <c r="G3">
-        <v>-9.891739073642599</v>
+        <v>-6.76384957395516</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-3.676138355343311</v>
       </c>
       <c r="E4">
-        <v>-19.18687926724045</v>
+        <v>-15.28275502795562</v>
       </c>
       <c r="F4">
-        <v>-3.251033222194323</v>
+        <v>-4.365054011807808</v>
       </c>
       <c r="G4">
-        <v>-9.704017899383766</v>
+        <v>-6.821933095441673</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-3.503218076456822</v>
       </c>
       <c r="E5">
-        <v>-19.08975255672394</v>
+        <v>-16.66793371436985</v>
       </c>
       <c r="F5">
-        <v>-3.339053885680993</v>
+        <v>-4.317925705160335</v>
       </c>
       <c r="G5">
-        <v>-9.639260318090082</v>
+        <v>-6.702763387664528</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.25912969690838</v>
       </c>
       <c r="E6">
-        <v>-19.05238358921265</v>
+        <v>-16.22359984473723</v>
       </c>
       <c r="F6">
-        <v>-3.704961991580396</v>
+        <v>-4.128224599714832</v>
       </c>
       <c r="G6">
-        <v>-9.529591876010645</v>
+        <v>-6.372218657750457</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-2.944864188873463</v>
       </c>
       <c r="E7">
-        <v>-19.64880172991886</v>
+        <v>-17.48362509500147</v>
       </c>
       <c r="F7">
-        <v>-3.413148036391798</v>
+        <v>-4.183842843873596</v>
       </c>
       <c r="G7">
-        <v>-9.474636820058743</v>
+        <v>-6.525582990402734</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-2.565300724510548</v>
       </c>
       <c r="E8">
-        <v>-21.48949961676465</v>
+        <v>-17.67890195116023</v>
       </c>
       <c r="F8">
-        <v>-3.772349679798136</v>
+        <v>-4.334253655036917</v>
       </c>
       <c r="G8">
-        <v>-8.975952792750627</v>
+        <v>-5.2352482082887</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-2.131088898087999</v>
       </c>
       <c r="E9">
-        <v>-20.86847827677476</v>
+        <v>-17.71952236300903</v>
       </c>
       <c r="F9">
-        <v>-3.663624801445895</v>
+        <v>-4.234712057712111</v>
       </c>
       <c r="G9">
-        <v>-8.98180583726406</v>
+        <v>-5.79631946628438</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-1.650435016270563</v>
       </c>
       <c r="E10">
-        <v>-22.27023117805706</v>
+        <v>-19.49364262499405</v>
       </c>
       <c r="F10">
-        <v>-3.637826127053108</v>
+        <v>-4.349611586684819</v>
       </c>
       <c r="G10">
-        <v>-7.414947807345782</v>
+        <v>-4.442908860010613</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-1.136742381437887</v>
       </c>
       <c r="E11">
-        <v>-22.38926211734867</v>
+        <v>-20.12120760992503</v>
       </c>
       <c r="F11">
-        <v>-3.851178778583343</v>
+        <v>-4.399417176778139</v>
       </c>
       <c r="G11">
-        <v>-7.599699422255889</v>
+        <v>-4.728479828773684</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-0.6058141880625735</v>
       </c>
       <c r="E12">
-        <v>-22.4507995506389</v>
+        <v>-20.6416787130486</v>
       </c>
       <c r="F12">
-        <v>-3.447483865237837</v>
+        <v>-4.438515289822873</v>
       </c>
       <c r="G12">
-        <v>-5.834874079634733</v>
+        <v>-4.293391381274969</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-0.06840405971114255</v>
       </c>
       <c r="E13">
-        <v>-24.53883815930963</v>
+        <v>-20.78846919800724</v>
       </c>
       <c r="F13">
-        <v>-3.328672785389109</v>
+        <v>-4.382099327855213</v>
       </c>
       <c r="G13">
-        <v>-6.738782123131799</v>
+        <v>-3.866969941998065</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>0.4583125988587354</v>
       </c>
       <c r="E14">
-        <v>-23.5663891224285</v>
+        <v>-21.14644053983957</v>
       </c>
       <c r="F14">
-        <v>-3.59346291079618</v>
+        <v>-3.990482011242524</v>
       </c>
       <c r="G14">
-        <v>-5.127850800449203</v>
+        <v>-3.268704704868672</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>0.961062926303191</v>
       </c>
       <c r="E15">
-        <v>-26.35231991736932</v>
+        <v>-22.83662100761841</v>
       </c>
       <c r="F15">
-        <v>-3.506525751872372</v>
+        <v>-4.016430620135218</v>
       </c>
       <c r="G15">
-        <v>-6.268562166370337</v>
+        <v>-3.219129285418086</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>1.432219644665459</v>
       </c>
       <c r="E16">
-        <v>-24.93773784922329</v>
+        <v>-22.55726397455923</v>
       </c>
       <c r="F16">
-        <v>-3.096374542989447</v>
+        <v>-4.025646207491363</v>
       </c>
       <c r="G16">
-        <v>-4.741655800019984</v>
+        <v>-2.172483760449804</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>1.86205517219775</v>
       </c>
       <c r="E17">
-        <v>-26.96296652340764</v>
+        <v>-24.0700505300356</v>
       </c>
       <c r="F17">
-        <v>-3.068214193131278</v>
+        <v>-3.626240580557554</v>
       </c>
       <c r="G17">
-        <v>-4.358178757478506</v>
+        <v>-2.425955679664103</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>2.245559223589032</v>
       </c>
       <c r="E18">
-        <v>-27.43080317314006</v>
+        <v>-25.13491666446528</v>
       </c>
       <c r="F18">
-        <v>-2.99065995177898</v>
+        <v>-3.855411736011648</v>
       </c>
       <c r="G18">
-        <v>-5.28307897024009</v>
+        <v>-1.625485631541565</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>2.577171796451857</v>
       </c>
       <c r="E19">
-        <v>-27.79916736282</v>
+        <v>-25.63851014496227</v>
       </c>
       <c r="F19">
-        <v>-2.746772849414152</v>
+        <v>-3.416732382143711</v>
       </c>
       <c r="G19">
-        <v>-4.159046132745805</v>
+        <v>-1.99920980692435</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>2.849026859288236</v>
       </c>
       <c r="E20">
-        <v>-27.86316828597041</v>
+        <v>-26.08585544980998</v>
       </c>
       <c r="F20">
-        <v>-2.990346828900722</v>
+        <v>-3.466032668121323</v>
       </c>
       <c r="G20">
-        <v>-3.965713583797907</v>
+        <v>-1.126881057326393</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>3.05314332105735</v>
       </c>
       <c r="E21">
-        <v>-29.17712313319199</v>
+        <v>-26.03536296462446</v>
       </c>
       <c r="F21">
-        <v>-2.380186310611856</v>
+        <v>-3.269524867727017</v>
       </c>
       <c r="G21">
-        <v>-3.497370706357212</v>
+        <v>-1.468810753350017</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>3.17685135198474</v>
       </c>
       <c r="E22">
-        <v>-29.08691140248519</v>
+        <v>-27.23646371110089</v>
       </c>
       <c r="F22">
-        <v>-3.175001520128371</v>
+        <v>-2.980953142552975</v>
       </c>
       <c r="G22">
-        <v>-4.480198844964963</v>
+        <v>-1.114112283181424</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>3.208895876213337</v>
       </c>
       <c r="E23">
-        <v>-30.63817640160473</v>
+        <v>-27.2193460793519</v>
       </c>
       <c r="F23">
-        <v>-2.724429295458441</v>
+        <v>-2.952063829380343</v>
       </c>
       <c r="G23">
-        <v>-3.568256107444086</v>
+        <v>-1.549124588132736</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>3.137323045646979</v>
       </c>
       <c r="E24">
-        <v>-29.61716174522833</v>
+        <v>-27.81657028843148</v>
       </c>
       <c r="F24">
-        <v>-2.857823783433454</v>
+        <v>-2.941622258268055</v>
       </c>
       <c r="G24">
-        <v>-3.744158634127722</v>
+        <v>-1.303945585494312</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>2.953284628859563</v>
       </c>
       <c r="E25">
-        <v>-29.96550102284635</v>
+        <v>-27.10838940921596</v>
       </c>
       <c r="F25">
-        <v>-2.645789892808475</v>
+        <v>-2.78176805871282</v>
       </c>
       <c r="G25">
-        <v>-3.894172694694257</v>
+        <v>-1.471005645042554</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>2.654472252886101</v>
       </c>
       <c r="E26">
-        <v>-30.49877185775261</v>
+        <v>-27.20008195092327</v>
       </c>
       <c r="F26">
-        <v>-2.672789699935322</v>
+        <v>-2.903404699772496</v>
       </c>
       <c r="G26">
-        <v>-3.330439758085002</v>
+        <v>-1.478315329593265</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.240860978218314</v>
       </c>
       <c r="E27">
-        <v>-29.99278507874256</v>
+        <v>-27.26230771226266</v>
       </c>
       <c r="F27">
-        <v>-2.816117141437304</v>
+        <v>-2.458552352018898</v>
       </c>
       <c r="G27">
-        <v>-3.567527787425447</v>
+        <v>-2.388682247437449</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>1.722904509797903</v>
       </c>
       <c r="E28">
-        <v>-30.49421621290089</v>
+        <v>-27.86126632688719</v>
       </c>
       <c r="F28">
-        <v>-2.668685967821854</v>
+        <v>-2.790180958055652</v>
       </c>
       <c r="G28">
-        <v>-4.604417134689497</v>
+        <v>-2.176489520552322</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.116031403770598</v>
       </c>
       <c r="E29">
-        <v>-31.10695497393075</v>
+        <v>-27.96560236802391</v>
       </c>
       <c r="F29">
-        <v>-2.664448868556534</v>
+        <v>-2.903522327943694</v>
       </c>
       <c r="G29">
-        <v>-4.362273902310585</v>
+        <v>-2.403778335096525</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.4401415234930574</v>
       </c>
       <c r="E30">
-        <v>-30.87756965154622</v>
+        <v>-26.96645344839354</v>
       </c>
       <c r="F30">
-        <v>-2.280256208975138</v>
+        <v>-2.771411809443021</v>
       </c>
       <c r="G30">
-        <v>-5.129098876117509</v>
+        <v>-2.772950510362812</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.2756943136555536</v>
       </c>
       <c r="E31">
-        <v>-29.77538889129334</v>
+        <v>-27.13910151993598</v>
       </c>
       <c r="F31">
-        <v>-2.466543612353704</v>
+        <v>-2.906048848522233</v>
       </c>
       <c r="G31">
-        <v>-5.320551035199101</v>
+        <v>-2.240879631291147</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.006005943498681</v>
       </c>
       <c r="E32">
-        <v>-29.14385243465764</v>
+        <v>-26.70632431597094</v>
       </c>
       <c r="F32">
-        <v>-2.680134833695946</v>
+        <v>-2.651005293976501</v>
       </c>
       <c r="G32">
-        <v>-4.478834900202783</v>
+        <v>-2.661391746780452</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.721721392465125</v>
       </c>
       <c r="E33">
-        <v>-29.11052286596118</v>
+        <v>-26.47760015079152</v>
       </c>
       <c r="F33">
-        <v>-2.869052303578401</v>
+        <v>-2.683945323748823</v>
       </c>
       <c r="G33">
-        <v>-4.451297782407126</v>
+        <v>-3.01884128029218</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.393596272040435</v>
       </c>
       <c r="E34">
-        <v>-29.01043453344365</v>
+        <v>-25.09845792022952</v>
       </c>
       <c r="F34">
-        <v>-2.759624141301184</v>
+        <v>-2.86823221984963</v>
       </c>
       <c r="G34">
-        <v>-4.488362650264806</v>
+        <v>-2.973692060227599</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.003473235779647</v>
       </c>
       <c r="E35">
-        <v>-28.47098006727992</v>
+        <v>-25.39290835715627</v>
       </c>
       <c r="F35">
-        <v>-2.351832122781432</v>
+        <v>-2.525293913662454</v>
       </c>
       <c r="G35">
-        <v>-5.679195675650505</v>
+        <v>-2.649986917397662</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.531471744646777</v>
       </c>
       <c r="E36">
-        <v>-26.3829459870832</v>
+        <v>-23.96723605616545</v>
       </c>
       <c r="F36">
-        <v>-2.196012900845234</v>
+        <v>-2.672662131355291</v>
       </c>
       <c r="G36">
-        <v>-4.901796819391149</v>
+        <v>-3.551471641559981</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.964615216675522</v>
       </c>
       <c r="E37">
-        <v>-28.03646845776994</v>
+        <v>-24.0050488141295</v>
       </c>
       <c r="F37">
-        <v>-2.393824551531547</v>
+        <v>-2.699591527252901</v>
       </c>
       <c r="G37">
-        <v>-5.156112927717961</v>
+        <v>-3.645971163978478</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.298985051842548</v>
       </c>
       <c r="E38">
-        <v>-25.14477515237997</v>
+        <v>-23.76216863920211</v>
       </c>
       <c r="F38">
-        <v>-2.186962158602246</v>
+        <v>-2.474546469832151</v>
       </c>
       <c r="G38">
-        <v>-6.305391985494729</v>
+        <v>-4.162237498645662</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.532971882145988</v>
       </c>
       <c r="E39">
-        <v>-25.62827126523093</v>
+        <v>-23.56808730018137</v>
       </c>
       <c r="F39">
-        <v>-2.251988999722007</v>
+        <v>-2.597807539368717</v>
       </c>
       <c r="G39">
-        <v>-5.924298535741526</v>
+        <v>-3.04845411014096</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.673461174892207</v>
       </c>
       <c r="E40">
-        <v>-24.90508302315398</v>
+        <v>-22.53540955899821</v>
       </c>
       <c r="F40">
-        <v>-2.351632486237357</v>
+        <v>-2.798166419818639</v>
       </c>
       <c r="G40">
-        <v>-5.181564401823879</v>
+        <v>-3.472981917369401</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.733958444380598</v>
       </c>
       <c r="E41">
-        <v>-23.01652822299514</v>
+        <v>-21.94884084925868</v>
       </c>
       <c r="F41">
-        <v>-2.075357875157875</v>
+        <v>-2.169438874563425</v>
       </c>
       <c r="G41">
-        <v>-6.441663971527749</v>
+        <v>-2.604404015867437</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.727452034257664</v>
       </c>
       <c r="E42">
-        <v>-23.61051004468523</v>
+        <v>-21.2697871148605</v>
       </c>
       <c r="F42">
-        <v>-1.979302876231452</v>
+        <v>-1.992182332610179</v>
       </c>
       <c r="G42">
-        <v>-6.055773541288143</v>
+        <v>-3.259114054441404</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.672765087553637</v>
       </c>
       <c r="E43">
-        <v>-24.6484544011393</v>
+        <v>-20.85630573864214</v>
       </c>
       <c r="F43">
-        <v>-2.358876559174839</v>
+        <v>-2.011677959435065</v>
       </c>
       <c r="G43">
-        <v>-6.853770611892844</v>
+        <v>-4.071823189422627</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.59075267972011</v>
       </c>
       <c r="E44">
-        <v>-23.70597480524093</v>
+        <v>-20.31931929081259</v>
       </c>
       <c r="F44">
-        <v>-1.969754285179382</v>
+        <v>-1.926397535316856</v>
       </c>
       <c r="G44">
-        <v>-5.736941521492013</v>
+        <v>-3.034612719241268</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.495571884833267</v>
       </c>
       <c r="E45">
-        <v>-21.48629345716722</v>
+        <v>-19.35447809026433</v>
       </c>
       <c r="F45">
-        <v>-1.550528311398789</v>
+        <v>-2.234317437918086</v>
       </c>
       <c r="G45">
-        <v>-6.492755620835321</v>
+        <v>-3.820420361170373</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.405201128852055</v>
       </c>
       <c r="E46">
-        <v>-21.98414936109649</v>
+        <v>-18.59535640693653</v>
       </c>
       <c r="F46">
-        <v>-1.666030891840735</v>
+        <v>-2.151953695425133</v>
       </c>
       <c r="G46">
-        <v>-6.172291502088331</v>
+        <v>-3.813925070822323</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.332591254967111</v>
       </c>
       <c r="E47">
-        <v>-21.18980520693702</v>
+        <v>-17.9678140643756</v>
       </c>
       <c r="F47">
-        <v>-1.787906931079821</v>
+        <v>-2.033237049460325</v>
       </c>
       <c r="G47">
-        <v>-5.926404042704503</v>
+        <v>-3.923795456179655</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.281605712041345</v>
       </c>
       <c r="E48">
-        <v>-20.61698041581077</v>
+        <v>-17.60475271775864</v>
       </c>
       <c r="F48">
-        <v>-1.393672801841688</v>
+        <v>-1.943363328093593</v>
       </c>
       <c r="G48">
-        <v>-6.926278180293962</v>
+        <v>-4.470985596729172</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.259842707991081</v>
       </c>
       <c r="E49">
-        <v>-20.39467762677423</v>
+        <v>-16.91038368426651</v>
       </c>
       <c r="F49">
-        <v>-1.30446011766239</v>
+        <v>-1.778158703483676</v>
       </c>
       <c r="G49">
-        <v>-6.656438923933506</v>
+        <v>-4.432070133915039</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.266118097959842</v>
       </c>
       <c r="E50">
-        <v>-18.53972863222631</v>
+        <v>-16.44607924426007</v>
       </c>
       <c r="F50">
-        <v>-2.035941669030465</v>
+        <v>-1.917065148156917</v>
       </c>
       <c r="G50">
-        <v>-7.317432377941009</v>
+        <v>-4.625101423218863</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.294072171471751</v>
       </c>
       <c r="E51">
-        <v>-18.04519662821867</v>
+        <v>-15.62272115713346</v>
       </c>
       <c r="F51">
-        <v>-1.410409965215252</v>
+        <v>-1.95394986350137</v>
       </c>
       <c r="G51">
-        <v>-7.411326070525819</v>
+        <v>-3.838744230730239</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.342345182700372</v>
       </c>
       <c r="E52">
-        <v>-17.99256217482751</v>
+        <v>-15.54775226993648</v>
       </c>
       <c r="F52">
-        <v>-1.203333853496029</v>
+        <v>-1.638394070181135</v>
       </c>
       <c r="G52">
-        <v>-6.918720204827806</v>
+        <v>-4.726304800354383</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.398948735505289</v>
       </c>
       <c r="E53">
-        <v>-17.66678828318971</v>
+        <v>-14.21336947646629</v>
       </c>
       <c r="F53">
-        <v>-1.196175930768439</v>
+        <v>-2.071123260994763</v>
       </c>
       <c r="G53">
-        <v>-7.836674893047999</v>
+        <v>-4.947995482391678</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.454786044701953</v>
       </c>
       <c r="E54">
-        <v>-17.5800498920468</v>
+        <v>-14.50361748951392</v>
       </c>
       <c r="F54">
-        <v>-1.655560327869349</v>
+        <v>-1.692319131368577</v>
       </c>
       <c r="G54">
-        <v>-8.158132175456771</v>
+        <v>-5.33136327693036</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.505529431462501</v>
       </c>
       <c r="E55">
-        <v>-16.45721929031894</v>
+        <v>-14.5490652546549</v>
       </c>
       <c r="F55">
-        <v>-1.429517916095629</v>
+        <v>-1.755205471119505</v>
       </c>
       <c r="G55">
-        <v>-7.401768525553943</v>
+        <v>-4.868433141446374</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.539432502380583</v>
       </c>
       <c r="E56">
-        <v>-16.84644615975222</v>
+        <v>-14.34315554152612</v>
       </c>
       <c r="F56">
-        <v>-1.489804838936571</v>
+        <v>-1.875176265332151</v>
       </c>
       <c r="G56">
-        <v>-8.282367017908999</v>
+        <v>-5.280311354169259</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.553294999622241</v>
       </c>
       <c r="E57">
-        <v>-15.83051924392343</v>
+        <v>-14.04486495864088</v>
       </c>
       <c r="F57">
-        <v>-1.157901214922088</v>
+        <v>-1.842302504952053</v>
       </c>
       <c r="G57">
-        <v>-7.139454139204251</v>
+        <v>-5.216411204170247</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.544641498743483</v>
       </c>
       <c r="E58">
-        <v>-15.88931695043902</v>
+        <v>-13.08024112484499</v>
       </c>
       <c r="F58">
-        <v>-1.689882074469541</v>
+        <v>-1.776303160501405</v>
       </c>
       <c r="G58">
-        <v>-8.301035184204951</v>
+        <v>-4.593042100216561</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.507924008804426</v>
       </c>
       <c r="E59">
-        <v>-15.9374184013485</v>
+        <v>-12.09186544487888</v>
       </c>
       <c r="F59">
-        <v>-1.663568155552212</v>
+        <v>-1.654293754110469</v>
       </c>
       <c r="G59">
-        <v>-8.373738074792884</v>
+        <v>-5.378584898502525</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.44533271554045</v>
       </c>
       <c r="E60">
-        <v>-16.06190615181935</v>
+        <v>-12.15196282343467</v>
       </c>
       <c r="F60">
-        <v>-1.860023768800143</v>
+        <v>-1.459349083005244</v>
       </c>
       <c r="G60">
-        <v>-8.277202566867738</v>
+        <v>-6.052251120834358</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.355630297572646</v>
       </c>
       <c r="E61">
-        <v>-14.39306385356466</v>
+        <v>-11.93653425794177</v>
       </c>
       <c r="F61">
-        <v>-1.503938443563136</v>
+        <v>-1.473563867637284</v>
       </c>
       <c r="G61">
-        <v>-8.246808448271688</v>
+        <v>-5.755020410681973</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.236328898157349</v>
       </c>
       <c r="E62">
-        <v>-15.71048751187612</v>
+        <v>-11.57396198651765</v>
       </c>
       <c r="F62">
-        <v>-1.134166832097076</v>
+        <v>-1.770382818673597</v>
       </c>
       <c r="G62">
-        <v>-7.89426514324916</v>
+        <v>-6.027084353644818</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.091707641752928</v>
       </c>
       <c r="E63">
-        <v>-14.30488993616131</v>
+        <v>-11.78065965412375</v>
       </c>
       <c r="F63">
-        <v>-1.714798537578347</v>
+        <v>-1.891674030526306</v>
       </c>
       <c r="G63">
-        <v>-8.359416654789998</v>
+        <v>-5.759218182425768</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.920173563223785</v>
       </c>
       <c r="E64">
-        <v>-14.73730486220574</v>
+        <v>-10.72384061800571</v>
       </c>
       <c r="F64">
-        <v>-1.683740558545186</v>
+        <v>-1.689104237478313</v>
       </c>
       <c r="G64">
-        <v>-9.066592219070333</v>
+        <v>-5.555235608478035</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.722497669864498</v>
       </c>
       <c r="E65">
-        <v>-14.3946805187854</v>
+        <v>-11.54304156599327</v>
       </c>
       <c r="F65">
-        <v>-1.968033766083768</v>
+        <v>-2.012174979876745</v>
       </c>
       <c r="G65">
-        <v>-8.498168239431932</v>
+        <v>-5.847563400686759</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.503972667871745</v>
       </c>
       <c r="E66">
-        <v>-14.30750286566374</v>
+        <v>-11.22832620788221</v>
       </c>
       <c r="F66">
-        <v>-2.009686564198735</v>
+        <v>-1.809551342947569</v>
       </c>
       <c r="G66">
-        <v>-8.49463257679599</v>
+        <v>-6.171066600238801</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.264607873087951</v>
       </c>
       <c r="E67">
-        <v>-14.61348732588801</v>
+        <v>-10.13023465965825</v>
       </c>
       <c r="F67">
-        <v>-1.85615860649868</v>
+        <v>-1.862571826931154</v>
       </c>
       <c r="G67">
-        <v>-8.469700858339738</v>
+        <v>-6.314323837359683</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.007993427996374</v>
       </c>
       <c r="E68">
-        <v>-13.28790788588874</v>
+        <v>-10.67179033776154</v>
       </c>
       <c r="F68">
-        <v>-2.288722123831749</v>
+        <v>-1.958874507711013</v>
       </c>
       <c r="G68">
-        <v>-9.316276874187706</v>
+        <v>-5.940599661976898</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.738260537675913</v>
       </c>
       <c r="E69">
-        <v>-13.09256310261986</v>
+        <v>-10.70339908633508</v>
       </c>
       <c r="F69">
-        <v>-1.908674614733961</v>
+        <v>-1.807420781987569</v>
       </c>
       <c r="G69">
-        <v>-7.799480913914287</v>
+        <v>-5.534389103217245</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.455361196736396</v>
       </c>
       <c r="E70">
-        <v>-13.50791473860339</v>
+        <v>-10.75897251935721</v>
       </c>
       <c r="F70">
-        <v>-2.051407288440732</v>
+        <v>-2.084218921265621</v>
       </c>
       <c r="G70">
-        <v>-7.210875848668488</v>
+        <v>-5.924073418644856</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.164299251728816</v>
       </c>
       <c r="E71">
-        <v>-12.89277135787546</v>
+        <v>-11.01268933258496</v>
       </c>
       <c r="F71">
-        <v>-1.912162869867149</v>
+        <v>-1.959574478166379</v>
       </c>
       <c r="G71">
-        <v>-8.592700867305821</v>
+        <v>-5.653863381184002</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.868214048197707</v>
       </c>
       <c r="E72">
-        <v>-13.28394094265802</v>
+        <v>-10.6338054977852</v>
       </c>
       <c r="F72">
-        <v>-2.270156753600206</v>
+        <v>-1.938855352687558</v>
       </c>
       <c r="G72">
-        <v>-7.977184377371286</v>
+        <v>-5.193916047230899</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.566517198869646</v>
       </c>
       <c r="E73">
-        <v>-14.83968460257115</v>
+        <v>-10.26926334016774</v>
       </c>
       <c r="F73">
-        <v>-2.010060986264801</v>
+        <v>-1.953524911023734</v>
       </c>
       <c r="G73">
-        <v>-8.908129646287579</v>
+        <v>-5.642912096540093</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.264554308068713</v>
       </c>
       <c r="E74">
-        <v>-14.19564050072626</v>
+        <v>-11.59060412849584</v>
       </c>
       <c r="F74">
-        <v>-1.768424558133379</v>
+        <v>-2.430560160743497</v>
       </c>
       <c r="G74">
-        <v>-8.032122880595491</v>
+        <v>-5.514893300536476</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.9638665985869779</v>
       </c>
       <c r="E75">
-        <v>-15.3359962968638</v>
+        <v>-11.91347073982071</v>
       </c>
       <c r="F75">
-        <v>-2.305982815403882</v>
+        <v>-2.385370233818575</v>
       </c>
       <c r="G75">
-        <v>-8.144899924936304</v>
+        <v>-5.564323055983334</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.6649881005422807</v>
       </c>
       <c r="E76">
-        <v>-16.44155529872641</v>
+        <v>-11.46692244639834</v>
       </c>
       <c r="F76">
-        <v>-2.030529944787976</v>
+        <v>-2.055772784653485</v>
       </c>
       <c r="G76">
-        <v>-7.904620529696</v>
+        <v>-5.459160266382846</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.3727942635029631</v>
       </c>
       <c r="E77">
-        <v>-15.31083156680318</v>
+        <v>-12.2664562317706</v>
       </c>
       <c r="F77">
-        <v>-2.347372192684759</v>
+        <v>-2.432139857380635</v>
       </c>
       <c r="G77">
-        <v>-7.302634239380467</v>
+        <v>-5.088998238000316</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-0.08892264303866486</v>
       </c>
       <c r="E78">
-        <v>-15.85975054364294</v>
+        <v>-12.37720006362818</v>
       </c>
       <c r="F78">
-        <v>-1.960561892110516</v>
+        <v>-2.25434819008518</v>
       </c>
       <c r="G78">
-        <v>-7.604201764189297</v>
+        <v>-4.846712652163216</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.1826088682644868</v>
       </c>
       <c r="E79">
-        <v>-16.19338586615806</v>
+        <v>-13.36508666840147</v>
       </c>
       <c r="F79">
-        <v>-2.645485053604245</v>
+        <v>-2.484224286199057</v>
       </c>
       <c r="G79">
-        <v>-6.514985934131527</v>
+        <v>-5.371192450313332</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.4360916926247506</v>
       </c>
       <c r="E80">
-        <v>-16.6478906884119</v>
+        <v>-13.62428293517849</v>
       </c>
       <c r="F80">
-        <v>-2.493754653168265</v>
+        <v>-2.657046577445118</v>
       </c>
       <c r="G80">
-        <v>-6.20999861578063</v>
+        <v>-4.851774476292761</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.667894970919357</v>
       </c>
       <c r="E81">
-        <v>-17.07598997872702</v>
+        <v>-14.63366620606619</v>
       </c>
       <c r="F81">
-        <v>-2.827450035875004</v>
+        <v>-2.796440930518608</v>
       </c>
       <c r="G81">
-        <v>-7.565041321005259</v>
+        <v>-4.288938697524649</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.8710758915464754</v>
       </c>
       <c r="E82">
-        <v>-18.42348270444941</v>
+        <v>-15.30964057813916</v>
       </c>
       <c r="F82">
-        <v>-3.061969131281572</v>
+        <v>-2.66239120392798</v>
       </c>
       <c r="G82">
-        <v>-6.221585525168079</v>
+        <v>-4.532128062293971</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>1.039515038247238</v>
       </c>
       <c r="E83">
-        <v>-18.43214114675207</v>
+        <v>-15.62555598186226</v>
       </c>
       <c r="F83">
-        <v>-2.885116832620892</v>
+        <v>-2.81194962503382</v>
       </c>
       <c r="G83">
-        <v>-7.273892083008515</v>
+        <v>-4.581494917375583</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>1.16888496432425</v>
       </c>
       <c r="E84">
-        <v>-21.04766546478427</v>
+        <v>-16.56134702165131</v>
       </c>
       <c r="F84">
-        <v>-3.147739948902239</v>
+        <v>-2.914269566627615</v>
       </c>
       <c r="G84">
-        <v>-7.336593815522311</v>
+        <v>-4.226558087928162</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>1.253144379914212</v>
       </c>
       <c r="E85">
-        <v>-20.59991259727586</v>
+        <v>-17.25721498003998</v>
       </c>
       <c r="F85">
-        <v>-3.10914631160581</v>
+        <v>-2.958208658774309</v>
       </c>
       <c r="G85">
-        <v>-6.053277389951532</v>
+        <v>-4.042594382856401</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>1.289710701556842</v>
       </c>
       <c r="E86">
-        <v>-20.9019799274835</v>
+        <v>-18.99032990988554</v>
       </c>
       <c r="F86">
-        <v>-3.489643624203318</v>
+        <v>-3.151218263626594</v>
       </c>
       <c r="G86">
-        <v>-5.215841790337493</v>
+        <v>-3.615133432280166</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>1.276282866040891</v>
       </c>
       <c r="E87">
-        <v>-22.06813444004274</v>
+        <v>-19.19623056606629</v>
       </c>
       <c r="F87">
-        <v>-3.484443962015945</v>
+        <v>-3.566734808177451</v>
       </c>
       <c r="G87">
-        <v>-6.101743776646462</v>
+        <v>-3.484595311121164</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>1.212117035225831</v>
       </c>
       <c r="E88">
-        <v>-23.04021667052926</v>
+        <v>-20.31175221074577</v>
       </c>
       <c r="F88">
-        <v>-3.497788132507643</v>
+        <v>-3.316996118479248</v>
       </c>
       <c r="G88">
-        <v>-6.298668267504469</v>
+        <v>-3.794929160517985</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>1.098627746366152</v>
       </c>
       <c r="E89">
-        <v>-24.88229121347338</v>
+        <v>-21.11136298017616</v>
       </c>
       <c r="F89">
-        <v>-3.5948595382373</v>
+        <v>-3.483547668486116</v>
       </c>
       <c r="G89">
-        <v>-5.60913128985737</v>
+        <v>-3.390350700709192</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>0.9370438147721821</v>
       </c>
       <c r="E90">
-        <v>-25.22517820838616</v>
+        <v>-23.76487666665869</v>
       </c>
       <c r="F90">
-        <v>-3.903215162092402</v>
+        <v>-3.799217776507938</v>
       </c>
       <c r="G90">
-        <v>-5.148564883888423</v>
+        <v>-3.516952583222001</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>0.7320176102854421</v>
       </c>
       <c r="E91">
-        <v>-26.95265518809217</v>
+        <v>-24.89193686310972</v>
       </c>
       <c r="F91">
-        <v>-3.191835602488062</v>
+        <v>-4.240077393380044</v>
       </c>
       <c r="G91">
-        <v>-4.696324499950744</v>
+        <v>-2.963853118884885</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>0.4872940239807302</v>
       </c>
       <c r="E92">
-        <v>-29.4881998624379</v>
+        <v>-26.42228031231382</v>
       </c>
       <c r="F92">
-        <v>-3.371341990307312</v>
+        <v>-4.094283902119927</v>
       </c>
       <c r="G92">
-        <v>-5.505584046480046</v>
+        <v>-3.616123285396409</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>0.2072589852878479</v>
       </c>
       <c r="E93">
-        <v>-30.2495065344744</v>
+        <v>-29.11988322173504</v>
       </c>
       <c r="F93">
-        <v>-4.284482856374513</v>
+        <v>-4.429337807367258</v>
       </c>
       <c r="G93">
-        <v>-5.047606487122809</v>
+        <v>-3.263245615274414</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.1001840172143606</v>
       </c>
       <c r="E94">
-        <v>-32.85156317080778</v>
+        <v>-30.47957112796009</v>
       </c>
       <c r="F94">
-        <v>-4.465071920389223</v>
+        <v>-4.348706181113559</v>
       </c>
       <c r="G94">
-        <v>-6.197494685278802</v>
+        <v>-3.24082329033693</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.4304284879214239</v>
       </c>
       <c r="E95">
-        <v>-34.58826918054142</v>
+        <v>-32.40999619879385</v>
       </c>
       <c r="F95">
-        <v>-4.355043191744976</v>
+        <v>-4.880702779641666</v>
       </c>
       <c r="G95">
-        <v>-6.048592968013463</v>
+        <v>-3.662666245133022</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.778112543014952</v>
       </c>
       <c r="E96">
-        <v>-36.91417494341306</v>
+        <v>-33.93859618550501</v>
       </c>
       <c r="F96">
-        <v>-4.863617701958926</v>
+        <v>-5.067704235721446</v>
       </c>
       <c r="G96">
-        <v>-5.902359550452776</v>
+        <v>-4.120461724485599</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.131884512788018</v>
       </c>
       <c r="E97">
-        <v>-38.46825212489136</v>
+        <v>-36.2667842992765</v>
       </c>
       <c r="F97">
-        <v>-4.691313968707018</v>
+        <v>-5.50382310594733</v>
       </c>
       <c r="G97">
-        <v>-6.141165752928103</v>
+        <v>-3.99949439048063</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.493150597455846</v>
       </c>
       <c r="E98">
-        <v>-40.67757006019852</v>
+        <v>-38.21412095629191</v>
       </c>
       <c r="F98">
-        <v>-6.064979893788784</v>
+        <v>-5.658452792293108</v>
       </c>
       <c r="G98">
-        <v>-7.182368741029824</v>
+        <v>-4.281744882067812</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.844484943267544</v>
       </c>
       <c r="E99">
-        <v>-40.46563521240255</v>
+        <v>-40.53216302404923</v>
       </c>
       <c r="F99">
-        <v>-5.53149554740525</v>
+        <v>-6.007840767078481</v>
       </c>
       <c r="G99">
-        <v>-7.556705367337374</v>
+        <v>-4.999302317159303</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.195179830656662</v>
       </c>
       <c r="E100">
-        <v>-43.69347940761889</v>
+        <v>-42.91023227901522</v>
       </c>
       <c r="F100">
-        <v>-5.806117565516148</v>
+        <v>-6.456492421925019</v>
       </c>
       <c r="G100">
-        <v>-8.124268605135565</v>
+        <v>-5.404685239534139</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.516059782234915</v>
       </c>
       <c r="E101">
-        <v>-45.7668050042387</v>
+        <v>-45.05340505872934</v>
       </c>
       <c r="F101">
-        <v>-6.029851317338267</v>
+        <v>-6.520954730659772</v>
       </c>
       <c r="G101">
-        <v>-6.997865417035162</v>
+        <v>-5.162018940960022</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.841304932145645</v>
       </c>
       <c r="E102">
-        <v>-47.35719149031051</v>
+        <v>-47.33963006810876</v>
       </c>
       <c r="F102">
-        <v>-6.26985213403286</v>
+        <v>-6.797424008078913</v>
       </c>
       <c r="G102">
-        <v>-8.236926469836964</v>
+        <v>-5.828815781297867</v>
       </c>
     </row>
   </sheetData>
